--- a/data/gravel/Canyon Grail 2025.xlsx
+++ b/data/gravel/Canyon Grail 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D803D5D1-CE9C-8740-8855-C16A9AB0F604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A897AB6D-B7C7-7849-B720-2FA4071BD63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="580" windowWidth="28040" windowHeight="15660" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
   <si>
     <t>brand</t>
   </si>
@@ -742,8 +742,8 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
+      <c r="B4" s="2">
+        <v>45853</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">

--- a/data/gravel/Canyon Grail 2025.xlsx
+++ b/data/gravel/Canyon Grail 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F63328-8EB4-2A49-A281-7EDDE98B7956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA237A7-94E3-E94C-AF50-382B0555402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20320" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -328,9 +328,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -347,17 +344,26 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -380,8 +386,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1379,26 +1386,26 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" t="s">
         <v>103</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
         <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
         <v>107</v>
-      </c>
-      <c r="B38" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1447,9 +1454,6 @@
       <c r="A45" t="s">
         <v>71</v>
       </c>
-      <c r="B45" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -1611,8 +1615,8 @@
       <c r="A73" t="s">
         <v>101</v>
       </c>
-      <c r="B73" t="s">
-        <v>102</v>
+      <c r="B73" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Canyon Grail 2025.xlsx
+++ b/data/gravel/Canyon Grail 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA237A7-94E3-E94C-AF50-382B0555402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE5B4E7-B2AA-E14E-9C0B-C591C10B37E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20320" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39220" yWindow="-16640" windowWidth="20320" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://dma.canyon.com/image/upload/t_web-p5/w_1300,c_fit/b_rgb:F2F2F2/f_auto/q_auto/v1740749738/ECD141A7-082D-4C81-8B8FE5BBC937914B</t>
   </si>
 </sst>
 </file>
@@ -731,6 +734,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Canyon Grail 2025.xlsx
+++ b/data/gravel/Canyon Grail 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE5B4E7-B2AA-E14E-9C0B-C591C10B37E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A49550-E242-6342-882D-F78BBD69BBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39220" yWindow="-16640" windowWidth="20320" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>https://dma.canyon.com/image/upload/t_web-p5/w_1300,c_fit/b_rgb:F2F2F2/f_auto/q_auto/v1740749738/ECD141A7-082D-4C81-8B8FE5BBC937914B</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Koblenz, Germany</t>
   </si>
 </sst>
 </file>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1627,6 +1633,14 @@
         <v>108</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>110</v>
+      </c>
+      <c r="B74" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Canyon Grail 2025.xlsx
+++ b/data/gravel/Canyon Grail 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A49550-E242-6342-882D-F78BBD69BBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92290DA5-1532-EA49-91FA-BC5F2E766B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39220" yWindow="-16640" windowWidth="20320" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -356,6 +356,24 @@
   </si>
   <si>
     <t>Koblenz, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -694,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1491,153 +1509,183 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="B56" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B59" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>89</v>
-      </c>
-      <c r="B62" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="B68" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="B69" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="B73" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>98</v>
+      </c>
+      <c r="B77" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>110</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>111</v>
       </c>
     </row>
